--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104481_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104481_W3.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6944</v>
+        <v>6.5882</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3673</v>
+        <v>3.0398</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3271</v>
+        <v>3.5484</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0764</v>
+        <v>4.0674</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7058</v>
+        <v>3.6887</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3706</v>
+        <v>0.3787</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8199</v>
+        <v>3.7905</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9989</v>
+        <v>2.9712</v>
       </c>
       <c r="L2" t="n">
-        <v>0.821</v>
+        <v>0.8192</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2565</v>
+        <v>0.277</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8733</v>
+        <v>0.7665</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9084</v>
+        <v>0.6151</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0351</v>
+        <v>0.1513</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>S. DEKKER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1235</v>
+        <v>6.3464</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4847</v>
+        <v>2.0975</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6388</v>
+        <v>4.2489</v>
       </c>
       <c r="G3" t="n">
-        <v>2.404</v>
+        <v>4.8386</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8816</v>
+        <v>1.5425</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5224</v>
+        <v>3.2961</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8243</v>
+        <v>2.2116</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0087</v>
+        <v>0.1789</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8156</v>
+        <v>2.0327</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4203</v>
+        <v>2.627</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1272</v>
+        <v>1.3636</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2931</v>
+        <v>1.2634</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9197</v>
+        <v>0.2998</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3266</v>
+        <v>0.1136</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2463</v>
+        <v>0.1862</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3461</v>
+        <v>-0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1212</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2249</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. DEKKER</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.746</v>
+        <v>5.7745</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7718</v>
+        <v>3.4471</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9742</v>
+        <v>2.3274</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8506</v>
+        <v>2.4053</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5455</v>
+        <v>1.884</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3052</v>
+        <v>0.5213</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2406</v>
+        <v>2.8033</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1936</v>
+        <v>1.9995</v>
       </c>
       <c r="L4" t="n">
-        <v>2.047</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>2.61</v>
+        <v>-0.3981</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3519</v>
+        <v>-0.1155</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2582</v>
+        <v>-0.2826</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3049</v>
+        <v>0.5772</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2419</v>
+        <v>-0.3256</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0629</v>
+        <v>0.9028</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>2.3367</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.1075</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.569</v>
+        <v>4.7773</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4137</v>
+        <v>2.7536</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1552</v>
+        <v>2.0238</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9877</v>
+        <v>3.9223</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>2.1914</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7277</v>
+        <v>1.7309</v>
       </c>
       <c r="J5" t="n">
-        <v>2.803</v>
+        <v>2.7282</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0567</v>
+        <v>0.9858</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7463</v>
+        <v>1.7425</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1847</v>
+        <v>1.1941</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2033</v>
+        <v>1.2057</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>2.033</v>
+        <v>0.5089</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8771</v>
+        <v>0.253</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1559</v>
+        <v>0.2559</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2249</v>
+        <v>-1.2472</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5383</v>
+        <v>4.2521</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4188</v>
+        <v>1.5641</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1195</v>
+        <v>2.688</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9244</v>
+        <v>3.1578</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1919</v>
+        <v>2.191</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7326</v>
+        <v>0.9668</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7484</v>
+        <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9973</v>
+        <v>0.8274</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7512</v>
+        <v>0.6626</v>
       </c>
       <c r="M6" t="n">
-        <v>1.176</v>
+        <v>1.6678</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1946</v>
+        <v>1.3636</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0186</v>
+        <v>0.3043</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2794</v>
+        <v>0.6586</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1028</v>
+        <v>0.3505</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3823</v>
+        <v>0.3082</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2534</v>
+        <v>-0.7025</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2534</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6759</v>
+        <v>3.6949</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9855</v>
+        <v>1.9453</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6904</v>
+        <v>1.7497</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5905</v>
+        <v>0.5742</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4082</v>
+        <v>-2.415</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9986</v>
+        <v>2.9892</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8535</v>
+        <v>0.8143</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.9101</v>
+        <v>-2.9312</v>
       </c>
       <c r="L7" t="n">
-        <v>3.7636</v>
+        <v>3.7456</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.263</v>
+        <v>-0.2402</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.405</v>
+        <v>0.4378</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2662</v>
+        <v>0.2691</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1388</v>
+        <v>0.1688</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.4859</v>
+        <v>3.47</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9899</v>
+        <v>2.6649</v>
       </c>
       <c r="F8" t="n">
-        <v>2.496</v>
+        <v>0.8051</v>
       </c>
       <c r="G8" t="n">
-        <v>3.148</v>
+        <v>2.9744</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1831</v>
+        <v>2.2412</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9649</v>
+        <v>0.7331</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5002</v>
+        <v>2.7712</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8312</v>
+        <v>2.0265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.669</v>
+        <v>0.7447</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6478</v>
+        <v>0.2032</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3519</v>
+        <v>0.2148</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2959</v>
+        <v>-0.0116</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4952</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0892</v>
+        <v>0.9524</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2419</v>
+        <v>0.1716</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1527</v>
+        <v>0.7809</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7071</v>
+        <v>-0.2292</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0.8603</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7997</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>M. ALLEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8481</v>
+        <v>2.3811</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2406</v>
+        <v>2.2211</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6075</v>
+        <v>0.16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9165</v>
+        <v>1.0579</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6681</v>
+        <v>0.5944</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7516</v>
+        <v>0.4635</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4973</v>
+        <v>1.7879</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3853</v>
+        <v>1.1549</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>0.633</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5808</v>
+        <v>-0.73</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2828</v>
+        <v>-0.5604</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8636</v>
+        <v>-0.1695</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1364</v>
+        <v>0.0743</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U9" t="n">
-        <v>0.281</v>
+        <v>0.1372</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>1.4764</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>1.6342</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ALLEN</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8354</v>
+        <v>2.1194</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8821</v>
+        <v>1.4671</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0467</v>
+        <v>0.6523</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0515</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.593</v>
+        <v>1.6659</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4585</v>
+        <v>-0.746</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7946</v>
+        <v>1.4907</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1602</v>
+        <v>1.3789</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6344</v>
+        <v>0.1117</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7431</v>
+        <v>-0.5708</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5672</v>
+        <v>0.287</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1759</v>
+        <v>-0.8578</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4676</v>
+        <v>0.1312</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0502</v>
+        <v>0.3126</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4783</v>
+        <v>0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>1.639</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. MAURI</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4914</v>
+        <v>-0.3391</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6246</v>
+        <v>-0.6731</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1332</v>
+        <v>0.334</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6209</v>
+        <v>2.6468</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1486</v>
+        <v>1.1227</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5276999999999999</v>
+        <v>1.5241</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4159</v>
+        <v>2.1121</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7864</v>
+        <v>0.362</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3705</v>
+        <v>1.7501</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.205</v>
+        <v>0.5347</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3622</v>
+        <v>0.7608</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1573</v>
+        <v>-0.226</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0974</v>
+        <v>-0.3031</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2087</v>
+        <v>-0.5089</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1113</v>
+        <v>0.2058</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>F. MAURI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7443</v>
+        <v>-0.4334</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7768</v>
+        <v>-0.6341</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0326</v>
+        <v>0.2006</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6376</v>
+        <v>-0.6262</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1182</v>
+        <v>-1.1488</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5194</v>
+        <v>0.5226</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1175</v>
+        <v>-0.4249</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3637</v>
+        <v>-0.7896</v>
       </c>
       <c r="L12" t="n">
-        <v>1.7539</v>
+        <v>0.3647</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5201</v>
+        <v>-0.2012</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7546</v>
+        <v>-0.3592</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2345</v>
+        <v>0.1579</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7014</v>
+        <v>-0.0349</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6261</v>
+        <v>-0.2091</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.1743</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8443</v>
+        <v>-5.1903</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3816</v>
+        <v>-4.4215</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4626</v>
+        <v>-0.7688</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.3948</v>
+        <v>-3.411</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6275</v>
+        <v>-1.6366</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7673</v>
+        <v>-1.7744</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.9904</v>
+        <v>-3.0274</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.6735</v>
+        <v>-1.6934</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3169</v>
+        <v>-1.334</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4044</v>
+        <v>-0.3836</v>
       </c>
       <c r="N13" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9893</v>
+        <v>0.6469</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2571</v>
+        <v>-0.2559</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2463</v>
+        <v>0.9028</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>33.4365</v>
+        <v>33.4411</v>
       </c>
       <c r="E14" t="n">
-        <v>15.7714</v>
+        <v>15.47179999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>17.6652</v>
+        <v>17.9694</v>
       </c>
       <c r="G14" t="n">
-        <v>22.5715</v>
+        <v>22.5274</v>
       </c>
       <c r="H14" t="n">
-        <v>11.9629</v>
+        <v>11.9214</v>
       </c>
       <c r="I14" t="n">
-        <v>10.6087</v>
+        <v>10.6059</v>
       </c>
       <c r="J14" t="n">
-        <v>18.793</v>
+        <v>18.5475</v>
       </c>
       <c r="K14" t="n">
-        <v>6.625599999999999</v>
+        <v>6.4709</v>
       </c>
       <c r="L14" t="n">
-        <v>12.1676</v>
+        <v>12.0767</v>
       </c>
       <c r="M14" t="n">
-        <v>3.778499999999999</v>
+        <v>3.979899999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>5.337300000000001</v>
+        <v>5.450799999999998</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.5586</v>
+        <v>-1.4708</v>
       </c>
       <c r="P14" t="n">
-        <v>6.805099999999999</v>
+        <v>6.8291</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2075</v>
+        <v>-10.2435</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0124</v>
+        <v>17.0722</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7028</v>
+        <v>4.7156</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2118000000000002</v>
+        <v>0.2291999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>4.4911</v>
+        <v>4.486800000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6429000000000005</v>
+        <v>-0.6310000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>6.9741</v>
+        <v>6.9388</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.616899999999999</v>
+        <v>-7.5698</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7467</v>
+        <v>2.2801</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2385</v>
+        <v>3.6741</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4918</v>
+        <v>-1.394</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3804</v>
+        <v>1.3899</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5037</v>
+        <v>-1.494</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8841</v>
+        <v>2.8839</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7323</v>
+        <v>3.7116</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4471</v>
+        <v>-0.4589</v>
       </c>
       <c r="L15" t="n">
-        <v>4.1795</v>
+        <v>4.1705</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.352</v>
+        <v>-2.3218</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0566</v>
+        <v>-1.0351</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7446</v>
+        <v>-0.2091</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0253</v>
+        <v>-0.5532</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2806</v>
+        <v>0.3441</v>
       </c>
       <c r="V15" t="n">
-        <v>2.0183</v>
+        <v>2.0099</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3278</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8679</v>
+        <v>0.1071</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.1127</v>
+        <v>-2.4852</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9806</v>
+        <v>2.5924</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3197</v>
+        <v>-1.3248</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7862</v>
+        <v>-1.7973</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4665</v>
+        <v>0.4725</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.9252</v>
+        <v>-1.9437</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.0372</v>
+        <v>-2.0554</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6055</v>
+        <v>0.6189</v>
       </c>
       <c r="N16" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2802</v>
+        <v>0.5214</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1875</v>
+        <v>-0.5415</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4677</v>
+        <v>1.063</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2502</v>
+        <v>-1.656</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1141</v>
+        <v>-0.595</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1361</v>
+        <v>-1.061</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2734</v>
+        <v>-2.2728</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9299</v>
+        <v>-1.9337</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3439</v>
+        <v>-0.3532</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9294</v>
+        <v>-1.9196</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5513</v>
+        <v>-1.546</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1839</v>
+        <v>-0.2254</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4567</v>
+        <v>-0.0141</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.564</v>
+        <v>-1.984</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.5135</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7197</v>
+        <v>-1.4706</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5161</v>
+        <v>-2.5149</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0028</v>
+        <v>0.0056</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.5189</v>
+        <v>-2.5205</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0508</v>
+        <v>-1.0707</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1649</v>
+        <v>-1.1773</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4653</v>
+        <v>-1.4442</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0213</v>
+        <v>-0.4495</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8861</v>
+        <v>-0.5323</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1352</v>
+        <v>0.0827</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1787</v>
+        <v>-2.4038</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6134</v>
+        <v>-0.6218</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5653</v>
+        <v>-1.782</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7894</v>
+        <v>-0.7493</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5917</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8024</v>
+        <v>-1.5613</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4831</v>
+        <v>1.2566</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4573</v>
+        <v>1.6892</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9405</v>
+        <v>-0.4326</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2725</v>
+        <v>-2.0059</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1344</v>
+        <v>-0.8772</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0726</v>
+        <v>-0.4367</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3085</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3811</v>
+        <v>0.2744</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8741</v>
+        <v>0.3757</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>1.792</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0349</v>
+        <v>-1.4163</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3146</v>
+        <v>-3.6401</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0532</v>
+        <v>-2.1081</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2614</v>
+        <v>-1.5319</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.759</v>
+        <v>-0.7754</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7977</v>
+        <v>-1.583</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5567</v>
+        <v>0.8076</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2784</v>
+        <v>1.4742</v>
       </c>
       <c r="K20" t="n">
-        <v>1.697</v>
+        <v>-0.4621</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4186</v>
+        <v>1.9363</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0374</v>
+        <v>-2.2496</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8993</v>
+        <v>-1.1209</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3471</v>
+        <v>-0.3997</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1825</v>
+        <v>-0.7809</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1645</v>
+        <v>0.3812</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3793</v>
+        <v>-0.8716</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7997</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4205</v>
+        <v>-1.0293</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7632</v>
+        <v>-4.4915</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8722</v>
+        <v>-0.6591</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.891</v>
+        <v>-3.8324</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8816</v>
+        <v>-1.8777</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3246</v>
+        <v>-1.3268</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5273</v>
+        <v>0.5141</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7415</v>
+        <v>-0.7519</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4089</v>
+        <v>-2.3918</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7806</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6775</v>
+        <v>-0.4416</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1031</v>
+        <v>-0.073</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4205</v>
+        <v>-1.4163</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5131</v>
+        <v>-2.5058</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.888</v>
+        <v>-4.5954</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8716</v>
+        <v>-2.4022</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0164</v>
+        <v>-2.1932</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0748</v>
+        <v>-4.164</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5022</v>
+        <v>-1.7642</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5726</v>
+        <v>-2.3998</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3868</v>
+        <v>-1.9697</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3494</v>
+        <v>-0.4277</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>-1.542</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4615</v>
+        <v>-2.1943</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8516</v>
+        <v>-1.3365</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6099</v>
+        <v>-0.8578</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.9488</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7461</v>
+        <v>-0.5111</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5939</v>
+        <v>-0.3139</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8478</v>
+        <v>-0.1972</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6105</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.4498</v>
+        <v>1.2472</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.4846</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1287</v>
+        <v>-4.6248</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0734</v>
+        <v>-4.094</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0554</v>
+        <v>-0.5309</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1349</v>
+        <v>-4.1319</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8932</v>
+        <v>-1.89</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2417</v>
+        <v>-2.2419</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.2538</v>
+        <v>-3.2732</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7184</v>
+        <v>-1.7312</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8812</v>
+        <v>-0.8587</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6763</v>
+        <v>-0.1743</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0484</v>
+        <v>-0.0468</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6279</v>
+        <v>-0.1275</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4439</v>
+        <v>-5.07</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.97</v>
+        <v>-5.3492</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4739</v>
+        <v>0.2792</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1769</v>
+        <v>-4.0412</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7779</v>
+        <v>-2.0447</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.399</v>
+        <v>-1.9966</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9581</v>
+        <v>-2.6972</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4227</v>
+        <v>-1.7279</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5354</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2188</v>
+        <v>-1.3441</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3552</v>
+        <v>-0.3168</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8636</v>
+        <v>-1.0273</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3513</v>
+        <v>-0.5947</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9043</v>
+        <v>-0.8506</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.447</v>
+        <v>0.2559</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7649</v>
+        <v>0.9317</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2534</v>
+        <v>0.7025</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.4885</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5198</v>
+        <v>-5.7835</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.7644</v>
+        <v>-3.2024</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2445</v>
+        <v>-2.5811</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.0262</v>
+        <v>-2.0651</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.0403</v>
+        <v>-0.4999</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9859</v>
+        <v>-1.5653</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.6546</v>
+        <v>0.3712</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.7081</v>
+        <v>0.334</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.9464</v>
+        <v>0.0372</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3716</v>
+        <v>-2.4364</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3321</v>
+        <v>-0.8339</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0395</v>
+        <v>-1.6025</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.361</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0646</v>
+        <v>-0.1429</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3217</v>
+        <v>0.2993</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2571</v>
+        <v>-0.4422</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9320000000000001</v>
+        <v>-0.6162</v>
       </c>
       <c r="W25" t="n">
-        <v>0.7071</v>
+        <v>-0.4584</v>
       </c>
       <c r="X25" t="n">
-        <v>0.2249</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-33.4365</v>
+        <v>-31.8619</v>
       </c>
       <c r="E26" t="n">
-        <v>-18.0508</v>
+        <v>-18.3564</v>
       </c>
       <c r="F26" t="n">
-        <v>-15.3859</v>
+        <v>-13.5055</v>
       </c>
       <c r="G26" t="n">
-        <v>-22.5716</v>
+        <v>-22.5272</v>
       </c>
       <c r="H26" t="n">
-        <v>-11.9628</v>
+        <v>-11.9214</v>
       </c>
       <c r="I26" t="n">
-        <v>-10.6087</v>
+        <v>-10.606</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.7785</v>
+        <v>-3.98</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.337199999999999</v>
+        <v>-5.4507</v>
       </c>
       <c r="L26" t="n">
-        <v>1.558799999999999</v>
+        <v>1.470899999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-18.7931</v>
+        <v>-18.5475</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.625599999999999</v>
+        <v>-6.4707</v>
       </c>
       <c r="O26" t="n">
-        <v>-12.1674</v>
+        <v>-12.0767</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.804799999999999</v>
+        <v>-6.8288</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.0125</v>
+        <v>-17.0724</v>
       </c>
       <c r="R26" t="n">
-        <v>10.2076</v>
+        <v>10.2436</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.702999999999999</v>
+        <v>-3.1366</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.4912</v>
+        <v>-4.486800000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2117999999999999</v>
+        <v>1.3501</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6430999999999998</v>
+        <v>0.6311000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>7.231399999999999</v>
+        <v>7.182899999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.5884</v>
+        <v>-6.551600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104481_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104481_W3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.5698</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.4163</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0293</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.5058</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.4846</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104481_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-6.551600000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
